--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1129,26 +1129,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>※ 黄色の欄が入力欄。基準所得金額と基準額に対する割合は画面にすでに正しく表示されているため、入力も変更も不要。</t>
+          <t>※ 黄色の欄が入力欄。基準所得金額と基準額に対する割合は画面にすでに表示されているため、入力も変更も不要。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>※ 令和9〜11年度は「①標準段階区分・割合」の画面、令和12年度以降は同画面の「R12以降を入力する」ボタンの先。</t>
+          <t>※ ただし表示されている基準所得金額（第7段階120万円〜第13段階720万円）と標準割合は第9期の政令によるもの。第10期の政令が公布されて段階区分や割合が変わった場合は、システム側で更新される。公布後に画面を再確認する。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>※ 割合は公費による低所得者軽減の前の標準割合。小野町が実際に賦課する割合（第1段階0.285・第2段階0.485・第3段階0.685）ではない。軽減相当額は別枠の公費で補填されるため、基準額の算定では軽減前を用いる。</t>
+          <t>※ 令和9〜11年度は「①標準段階区分・割合」の画面、令和12年度以降は同画面の「R12以降を入力する」ボタンの先。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
+        <is>
+          <t>※ 割合は公費による低所得者軽減の前の標準割合。小野町が実際に賦課する割合（第1段階0.285・第2段階0.485・第3段階0.685）ではない。軽減相当額は別枠の公費で補填されるため、基準額の算定では軽減前を用いる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 「②保険料設定の弾力化を行う場合の入力」は、小野町が標準の13段階そのものであるため入力不要。誤って入力した場合は「標準段階に戻す」を押す。</t>
         </is>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>6,211円</t>
+          <t>6,156円</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>6,095円</t>
+          <t>6,048円</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>5,939円</t>
+          <t>5,887円</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>5,997円</t>
+          <t>5,950円</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>5,808円</t>
+          <t>5,761円</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
@@ -1623,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1745,7 +1745,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>保険料基準額（基金12,000千円取崩）</t>
+          <t>保険料基準額（基金105,000千円取崩）</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1755,122 +1755,148 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>5,950円</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
+          <t>5,188円</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>令和8年度末見込の半分</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>保険料基準額（基金210,000千円取崩）</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>4,328円</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>令和8年度末見込の全額</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
           <t>保険料基準額（基金35,000千円取崩）</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>5,761円</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>【年度別の調整交付金見込交付割合】</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>年度</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>後期高齢者加入割合補正係数</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>所得段階別加入割合補正係数</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>見込交付割合</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>令和9年度</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>0.9558</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0.9959047342433924</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>0.0610662786523381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>令和10年度</t>
+          <t>令和9年度</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.9802</v>
+        <v>0.9558</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>0.9959047342433924</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.05547726128376418</v>
+        <v>0.0610662786523381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>令和11年度</t>
+          <t>令和10年度</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1.0065</v>
+        <v>0.9802</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0.9959047342433924</v>
       </c>
       <c r="D13" s="11" t="n">
+        <v>0.05547726128376418</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1.0065</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9959047342433924</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>0.04945303354632588</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>※ 後期高齢者加入割合補正係数は受領した見える化ワークシート「5_保険料推計」96行の値。第10期の全国値が確定すると動く。</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>※ 第9期計画の公表値による検算：補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.9738。当時の9段階の構成に標準割合を当てると0.970で整合する（軽減後だと0.932で再現できない）。</t>
+          <t>※ 後期高齢者加入割合補正係数は受領した見える化ワークシート「5_保険料推計」96行の値。第10期の全国値が確定すると動く。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t>※ 第9期計画の公表値による検算：補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.9738。当時の9段階の構成に標準割合を当てると0.970で整合する（軽減後だと0.932で再現できない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>※ 同計画の調整交付金見込額216,070千円÷標準給付費見込額3,566,486千円＝6.058％。上の算式に補正係数0.974を入れると後期高齢者加入割合補正係数は0.980となり整合する。</t>
         </is>

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_所得段階別被保険者数_20260925.xlsx
@@ -1623,13 +1623,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1640,15 +1639,10 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>現行（誤り）</t>
+          <t>値</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>訂正後</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>出所・算式</t>
         </is>
@@ -1662,17 +1656,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>0.9523</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
           <t>0.9959</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>段階別構成比×割合の合計。現行は軽減後の賦課割合、訂正後は軽減前の標準割合を用いる</t>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>段階別構成比×軽減前の標準割合の合計</t>
         </is>
       </c>
     </row>
@@ -1684,17 +1673,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>6.148％</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
           <t>5.533％</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>（第1号被保険者負担割合＋5％）－第1号被保険者負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数。現行は第9期の公表値からの逆算</t>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>（第1号被保険者負担割合＋5％）－第1号被保険者負担割合×後期高齢者加入割合補正係数×所得段階別加入割合補正係数</t>
         </is>
       </c>
     </row>
@@ -1706,197 +1690,155 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>6,156円</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
           <t>6,048円</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>上の2つを入れ替えた結果</t>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>上の2つによる</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　うち補正係数だけを直した場合</t>
+          <t>保険料基準額（基金105,000千円取崩）</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>5,887円</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>片落ち。調整交付金の割合が古いまま</t>
+          <t>5,188円</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>令和8年度末見込の半分</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>保険料基準額（基金105,000千円取崩）</t>
+          <t>保険料基準額（基金210,000千円取崩）</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>5,188円</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>令和8年度末見込の半分</t>
+          <t>4,328円</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>令和8年度末見込の全額</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>保険料基準額（基金210,000千円取崩）</t>
+          <t>保険料基準額（基金35,000千円取崩）</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>4,328円</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>令和8年度末見込の全額</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>保険料基準額（基金35,000千円取崩）</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
           <t>5,761円</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【年度別の調整交付金見込交付割合】</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>【年度別の調整交付金見込交付割合】</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>後期高齢者加入割合補正係数</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>所得段階別加入割合補正係数</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>見込交付割合</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>年度</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>後期高齢者加入割合補正係数</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>所得段階別加入割合補正係数</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>見込交付割合</t>
-        </is>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0.9558</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9959047342433924</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>0.0610662786523381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>令和9年度</t>
+          <t>令和10年度</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.9558</v>
+        <v>0.9802</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>0.9959047342433924</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.0610662786523381</v>
+        <v>0.05547726128376418</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>令和10年度</t>
+          <t>令和11年度</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.9802</v>
+        <v>1.0065</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0.9959047342433924</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0.05547726128376418</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>令和11年度</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>1.0065</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>0.9959047342433924</v>
-      </c>
-      <c r="D14" s="11" t="n">
         <v>0.04945303354632588</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>※ 後期高齢者加入割合補正係数は受領した見える化ワークシート「5_保険料推計」96行の値。第10期の全国値が確定すると動く。</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>※ 後期高齢者加入割合補正係数は受領した見える化ワークシート「5_保険料推計」96行の値。第10期の全国値が確定すると動く。</t>
+          <t>※ 第9期計画の公表値による検算：補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.9738。当時の9段階の構成に標準割合を当てると0.970で整合する（軽減後だと0.932で再現できない）。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
-        <is>
-          <t>※ 第9期計画の公表値による検算：補正後被保険者数10,136人÷第1号被保険者数10,409人＝0.9738。当時の9段階の構成に標準割合を当てると0.970で整合する（軽減後だと0.932で再現できない）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
         <is>
           <t>※ 同計画の調整交付金見込額216,070千円÷標準給付費見込額3,566,486千円＝6.058％。上の算式に補正係数0.974を入れると後期高齢者加入割合補正係数は0.980となり整合する。</t>
         </is>
